--- a/Data/EC/NIT-9017497287.xlsx
+++ b/Data/EC/NIT-9017497287.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4B92725-AF66-44F1-88B7-2DDACFA54BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{075B1D5F-AC1A-4F6A-B7A1-9708FECF7F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C69A865F-AD17-48E5-9243-F5DED4FC4C7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{88BE81B8-7BE0-4466-ADC2-E39B0EBCA4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -74,6 +74,9 @@
     <t>JUAN PABLO VARGAS LOZANO</t>
   </si>
   <si>
+    <t>2607</t>
+  </si>
+  <si>
     <t>2606</t>
   </si>
   <si>
@@ -81,6 +84,12 @@
   </si>
   <si>
     <t>2604</t>
+  </si>
+  <si>
+    <t>1053006756</t>
+  </si>
+  <si>
+    <t>DAVID DANIEL GUTIERREZ BECERRA</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -479,22 +488,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2628FBCD-CB32-39D2-6143-099D28FBA5E0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1EDC80C-CBDC-58DD-9B08-BA72858BED39}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -503,7 +512,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -516,7 +525,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -845,27 +854,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8214DE4-7D1D-462B-85E5-7C347C0490A6}">
-  <dimension ref="B2:J24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1F78ED-3812-4AA1-AF0A-97ABCBFA35FA}">
+  <dimension ref="B2:J26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -874,7 +883,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -885,7 +894,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -896,7 +905,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -907,10 +916,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -923,8 +932,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -939,15 +948,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>210111</v>
+        <v>317501</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -955,27 +964,27 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F13" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -995,16 +1004,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1027,7 +1036,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1050,57 +1059,103 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B18" s="21" t="s">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="18">
         <v>70037</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="18">
         <v>1750905</v>
       </c>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="26"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B23" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="32"/>
-      <c r="H23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B24" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="32"/>
-      <c r="H24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="18">
+        <v>70037</v>
+      </c>
+      <c r="G19" s="18">
+        <v>1750905</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="24">
+        <v>37353</v>
+      </c>
+      <c r="G20" s="24">
+        <v>1750905</v>
+      </c>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="26"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="32"/>
+      <c r="H25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="32"/>
+      <c r="H26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="H25:J25"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
